--- a/globallbz1_p_ttl_7.xlsx
+++ b/globallbz1_p_ttl_7.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
         <v>30000</v>
@@ -705,10 +705,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B3" t="n">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="C3" t="n">
         <v>30000</v>
@@ -735,10 +735,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
         <v>30000</v>
@@ -765,10 +765,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C5" t="n">
         <v>30000</v>
@@ -793,6 +793,66 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B6" t="n">
+        <v>149</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5052</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5052</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/globallbz1_p_ttl_7.xlsx
+++ b/globallbz1_p_ttl_7.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,186 +673,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B2" t="n">
-        <v>79</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B4" t="n">
-        <v>79</v>
-      </c>
-      <c r="C4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B5" t="n">
-        <v>81</v>
-      </c>
-      <c r="C5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>49</v>
-      </c>
-      <c r="B6" t="n">
-        <v>149</v>
-      </c>
-      <c r="C6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
